--- a/URUVS/Datasheets/URUV/06.2024/June_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/06.2024/June_RecordingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sophi\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\06.2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\06.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92E2DB2-E703-4D40-B9DB-9C9A55D3AED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92DD4D42-54D5-4747-9418-97048918BBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-3840" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -19,17 +19,28 @@
     <sheet name="Metadata" sheetId="6" r:id="rId4"/>
     <sheet name="LATLON" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="241">
   <si>
     <t>DATE</t>
   </si>
@@ -716,6 +727,42 @@
   </si>
   <si>
     <t>T1_FISHP</t>
+  </si>
+  <si>
+    <t>MAXN_MUDCRAB</t>
+  </si>
+  <si>
+    <t>TIME_1STMUDCRAB</t>
+  </si>
+  <si>
+    <t>T1_MUDCRAB</t>
+  </si>
+  <si>
+    <t>MAXN_SWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>TIME_1STSWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>T1_SWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>MAXN_SHRIMP</t>
+  </si>
+  <si>
+    <t>TIME_SHRIMP</t>
+  </si>
+  <si>
+    <t>T1_SHRIMP</t>
+  </si>
+  <si>
+    <t>MAXN_ULAR</t>
+  </si>
+  <si>
+    <t>TIME_ULAR</t>
+  </si>
+  <si>
+    <t>T1_ULAR</t>
   </si>
 </sst>
 </file>
@@ -1426,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF2D75B-3330-44BB-BF8B-27BF0F133624}">
-  <dimension ref="A1:DI25"/>
+  <dimension ref="A1:DU25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.453125" bestFit="1" customWidth="1"/>
@@ -1451,10 +1498,14 @@
     <col min="106" max="106" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="109" max="109" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="112" max="112" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="113" max="113" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="124" max="124" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:113" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="93" t="s">
         <v>218</v>
       </c>
@@ -1791,11 +1842,47 @@
       <c r="DH1" s="59" t="s">
         <v>222</v>
       </c>
-      <c r="DI1" s="28" t="s">
+      <c r="DI1" s="81" t="s">
+        <v>229</v>
+      </c>
+      <c r="DJ1" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="DK1" s="59" t="s">
+        <v>231</v>
+      </c>
+      <c r="DL1" s="81" t="s">
+        <v>232</v>
+      </c>
+      <c r="DM1" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="DN1" s="59" t="s">
+        <v>234</v>
+      </c>
+      <c r="DO1" s="81" t="s">
+        <v>235</v>
+      </c>
+      <c r="DP1" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="DQ1" s="59" t="s">
+        <v>237</v>
+      </c>
+      <c r="DR1" s="81" t="s">
+        <v>238</v>
+      </c>
+      <c r="DS1" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="DT1" s="59" t="s">
+        <v>240</v>
+      </c>
+      <c r="DU1" s="28" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:113" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="94" t="s">
         <v>219</v>
       </c>
@@ -1895,8 +1982,12 @@
         <v>30</v>
       </c>
       <c r="AI2" s="99"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="30"/>
+      <c r="AJ2" s="32">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="30">
+        <v>0</v>
+      </c>
       <c r="AL2" s="31"/>
       <c r="AM2" s="34"/>
       <c r="AN2" s="33" t="str">
@@ -2044,12 +2135,40 @@
       <c r="DF2" s="58"/>
       <c r="DG2" s="71"/>
       <c r="DH2" s="33" t="str">
-        <f t="shared" ref="DH2:DH13" si="25">IF(DF2=0,"NA",DG2-$AD2)</f>
-        <v>NA</v>
-      </c>
-      <c r="DI2" s="35"/>
+        <f t="shared" ref="DH2:DH24" si="25">IF(DF2=0,"NA",DG2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DI2" s="58"/>
+      <c r="DJ2" s="71"/>
+      <c r="DK2" s="33" t="str">
+        <f t="shared" ref="DK2:DK24" si="26">IF(DI2=0,"NA",DJ2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DL2" s="58">
+        <v>1</v>
+      </c>
+      <c r="DM2" s="71">
+        <v>2.7534722222222221E-2</v>
+      </c>
+      <c r="DN2" s="33">
+        <f t="shared" ref="DN2:DN24" si="27">IF(DL2=0,"NA",DM2-$AD2)</f>
+        <v>1.7118055555555553E-2</v>
+      </c>
+      <c r="DO2" s="58"/>
+      <c r="DP2" s="71"/>
+      <c r="DQ2" s="33" t="str">
+        <f t="shared" ref="DQ2:DQ24" si="28">IF(DO2=0,"NA",DP2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DR2" s="58"/>
+      <c r="DS2" s="71"/>
+      <c r="DT2" s="33" t="str">
+        <f t="shared" ref="DT2:DT13" si="29">IF(DR2=0,"NA",DS2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DU2" s="35"/>
     </row>
-    <row r="3" spans="1:113" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="94" t="s">
         <v>219</v>
       </c>
@@ -2066,7 +2185,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="74" t="str">
-        <f t="shared" ref="F3:F25" si="26">D3&amp;""&amp;E3</f>
+        <f t="shared" ref="F3:F25" si="30">D3&amp;""&amp;E3</f>
         <v>D5</v>
       </c>
       <c r="G3" s="5">
@@ -2102,7 +2221,7 @@
         <v>3</v>
       </c>
       <c r="Q3" s="6">
-        <f t="shared" ref="Q3:Q24" si="27">J3-I3</f>
+        <f t="shared" ref="Q3:Q24" si="31">J3-I3</f>
         <v>7.4305555555555514E-2</v>
       </c>
       <c r="R3" s="6" t="s">
@@ -2127,7 +2246,7 @@
       <c r="AA3" s="20"/>
       <c r="AB3" s="20"/>
       <c r="AC3" s="20">
-        <f t="shared" ref="AC3:AC24" si="28">SUM(W3:AB3)</f>
+        <f t="shared" ref="AC3:AC24" si="32">SUM(W3:AB3)</f>
         <v>0</v>
       </c>
       <c r="AD3" s="20"/>
@@ -2291,9 +2410,37 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI3" s="35"/>
+      <c r="DI3" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ3" s="34">
+        <v>2.9837962962962962E-2</v>
+      </c>
+      <c r="DK3" s="33">
+        <f t="shared" si="26"/>
+        <v>2.9837962962962962E-2</v>
+      </c>
+      <c r="DL3" s="31"/>
+      <c r="DM3" s="32"/>
+      <c r="DN3" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO3" s="31"/>
+      <c r="DP3" s="32"/>
+      <c r="DQ3" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR3" s="31"/>
+      <c r="DS3" s="32"/>
+      <c r="DT3" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU3" s="35"/>
     </row>
-    <row r="4" spans="1:113" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="94" t="s">
         <v>219</v>
       </c>
@@ -2310,7 +2457,7 @@
         <v>5</v>
       </c>
       <c r="F4" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>E5</v>
       </c>
       <c r="G4" s="5">
@@ -2346,7 +2493,7 @@
         <v>3</v>
       </c>
       <c r="Q4" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>4.9305555555555547E-2</v>
       </c>
       <c r="R4" s="6" t="s">
@@ -2375,7 +2522,7 @@
       <c r="AA4" s="20"/>
       <c r="AB4" s="20"/>
       <c r="AC4" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>4.2789351851851849E-2</v>
       </c>
       <c r="AD4" s="20">
@@ -2397,7 +2544,7 @@
         <v>1</v>
       </c>
       <c r="AK4" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" s="31">
         <v>1</v>
@@ -2557,9 +2704,33 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI4" s="35"/>
+      <c r="DI4" s="31"/>
+      <c r="DJ4" s="34"/>
+      <c r="DK4" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL4" s="31"/>
+      <c r="DM4" s="34"/>
+      <c r="DN4" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO4" s="31"/>
+      <c r="DP4" s="34"/>
+      <c r="DQ4" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR4" s="31"/>
+      <c r="DS4" s="34"/>
+      <c r="DT4" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU4" s="35"/>
     </row>
-    <row r="5" spans="1:113" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="94" t="s">
         <v>219</v>
       </c>
@@ -2576,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>L5</v>
       </c>
       <c r="G5" s="5">
@@ -2612,7 +2783,7 @@
         <v>3</v>
       </c>
       <c r="Q5" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>7.7777777777777779E-2</v>
       </c>
       <c r="R5" s="6" t="s">
@@ -2637,7 +2808,7 @@
       <c r="AA5" s="20"/>
       <c r="AB5" s="20"/>
       <c r="AC5" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AD5" s="20"/>
@@ -2801,9 +2972,33 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI5" s="35"/>
+      <c r="DI5" s="31"/>
+      <c r="DJ5" s="32"/>
+      <c r="DK5" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL5" s="31"/>
+      <c r="DM5" s="34"/>
+      <c r="DN5" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO5" s="31"/>
+      <c r="DP5" s="34"/>
+      <c r="DQ5" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR5" s="31"/>
+      <c r="DS5" s="34"/>
+      <c r="DT5" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU5" s="35"/>
     </row>
-    <row r="6" spans="1:113" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="94" t="s">
         <v>219</v>
       </c>
@@ -2820,7 +3015,7 @@
         <v>4</v>
       </c>
       <c r="F6" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>E4</v>
       </c>
       <c r="G6" s="5">
@@ -2856,7 +3051,7 @@
         <v>4</v>
       </c>
       <c r="Q6" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>5.6944444444444464E-2</v>
       </c>
       <c r="R6" s="6" t="s">
@@ -2887,7 +3082,7 @@
       <c r="AA6" s="20"/>
       <c r="AB6" s="20"/>
       <c r="AC6" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.8356481481481474E-2</v>
       </c>
       <c r="AD6" s="20">
@@ -2908,10 +3103,10 @@
       </c>
       <c r="AI6" s="22"/>
       <c r="AJ6" s="32">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AK6" s="30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL6" s="31"/>
       <c r="AM6" s="34"/>
@@ -3051,17 +3246,21 @@
         <v>1</v>
       </c>
       <c r="CX6" s="34">
-        <v>2.4375000000000001E-2</v>
+        <v>2.3912037037037037E-2</v>
       </c>
       <c r="CY6" s="33">
         <f t="shared" si="22"/>
-        <v>1.8819444444444444E-2</v>
-      </c>
-      <c r="CZ6" s="31"/>
-      <c r="DA6" s="32"/>
-      <c r="DB6" s="33" t="str">
+        <v>1.8356481481481481E-2</v>
+      </c>
+      <c r="CZ6" s="31">
+        <v>2</v>
+      </c>
+      <c r="DA6" s="34">
+        <v>1.0625000000000001E-2</v>
+      </c>
+      <c r="DB6" s="33">
         <f t="shared" si="23"/>
-        <v>NA</v>
+        <v>5.069444444444445E-3</v>
       </c>
       <c r="DC6" s="31"/>
       <c r="DD6" s="32"/>
@@ -3075,9 +3274,41 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI6" s="35"/>
+      <c r="DI6" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ6" s="34">
+        <v>1.3553240740740741E-2</v>
+      </c>
+      <c r="DK6" s="33">
+        <f t="shared" si="26"/>
+        <v>7.9976851851851841E-3</v>
+      </c>
+      <c r="DL6" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM6" s="34">
+        <v>2.1655092592592594E-2</v>
+      </c>
+      <c r="DN6" s="33">
+        <f t="shared" si="27"/>
+        <v>1.6099537037037037E-2</v>
+      </c>
+      <c r="DO6" s="31"/>
+      <c r="DP6" s="32"/>
+      <c r="DQ6" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR6" s="31"/>
+      <c r="DS6" s="32"/>
+      <c r="DT6" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU6" s="35"/>
     </row>
-    <row r="7" spans="1:113" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="94" t="s">
         <v>219</v>
       </c>
@@ -3094,7 +3325,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>D4</v>
       </c>
       <c r="G7" s="5">
@@ -3130,7 +3361,7 @@
         <v>3</v>
       </c>
       <c r="Q7" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>7.9861111111111105E-2</v>
       </c>
       <c r="R7" s="6" t="s">
@@ -3159,7 +3390,7 @@
       <c r="AA7" s="20"/>
       <c r="AB7" s="20"/>
       <c r="AC7" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.9074074074074077E-2</v>
       </c>
       <c r="AD7" s="20">
@@ -3180,10 +3411,10 @@
       </c>
       <c r="AI7" s="22"/>
       <c r="AJ7" s="32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK7" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL7" s="31"/>
       <c r="AM7" s="34"/>
@@ -3237,11 +3468,11 @@
         <v>7</v>
       </c>
       <c r="BK7" s="34">
-        <v>1.0995370370370371E-2</v>
+        <v>5.5555555555555558E-3</v>
       </c>
       <c r="BL7" s="33">
         <f t="shared" si="9"/>
-        <v>5.4398148148148149E-3</v>
+        <v>0</v>
       </c>
       <c r="BM7" s="31"/>
       <c r="BN7" s="32"/>
@@ -3332,24 +3563,68 @@
         <v>9.4328703703703692E-3</v>
       </c>
       <c r="DC7" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DD7" s="34">
-        <v>3.9421296296296295E-2</v>
+        <v>1.2974537037037038E-2</v>
       </c>
       <c r="DE7" s="33">
         <f t="shared" si="24"/>
-        <v>3.3865740740740738E-2</v>
-      </c>
-      <c r="DF7" s="31"/>
-      <c r="DG7" s="34"/>
-      <c r="DH7" s="33" t="str">
+        <v>7.4189814814814821E-3</v>
+      </c>
+      <c r="DF7" s="31">
+        <v>1</v>
+      </c>
+      <c r="DG7" s="34">
+        <v>4.4386574074074071E-2</v>
+      </c>
+      <c r="DH7" s="33">
         <f t="shared" si="25"/>
-        <v>NA</v>
-      </c>
-      <c r="DI7" s="35"/>
+        <v>3.8831018518518515E-2</v>
+      </c>
+      <c r="DI7" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ7" s="34">
+        <v>2.4039351851851853E-2</v>
+      </c>
+      <c r="DK7" s="33">
+        <f t="shared" si="26"/>
+        <v>1.8483796296296297E-2</v>
+      </c>
+      <c r="DL7" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM7" s="34">
+        <v>6.145833333333333E-3</v>
+      </c>
+      <c r="DN7" s="33">
+        <f t="shared" si="27"/>
+        <v>5.9027777777777724E-4</v>
+      </c>
+      <c r="DO7" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP7" s="34">
+        <v>2.4953703703703704E-2</v>
+      </c>
+      <c r="DQ7" s="33">
+        <f t="shared" si="28"/>
+        <v>1.9398148148148147E-2</v>
+      </c>
+      <c r="DR7" s="31">
+        <v>1</v>
+      </c>
+      <c r="DS7" s="34">
+        <v>3.4872685185185187E-2</v>
+      </c>
+      <c r="DT7" s="33">
+        <f t="shared" si="29"/>
+        <v>2.931712962962963E-2</v>
+      </c>
+      <c r="DU7" s="35"/>
     </row>
-    <row r="8" spans="1:113" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="94" t="s">
         <v>219</v>
       </c>
@@ -3366,7 +3641,7 @@
         <v>6</v>
       </c>
       <c r="F8" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>L6</v>
       </c>
       <c r="G8" s="5">
@@ -3402,7 +3677,7 @@
         <v>4</v>
       </c>
       <c r="Q8" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>8.2638888888888873E-2</v>
       </c>
       <c r="R8" s="6" t="s">
@@ -3427,7 +3702,7 @@
       <c r="AA8" s="20"/>
       <c r="AB8" s="20"/>
       <c r="AC8" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AD8" s="20"/>
@@ -3591,9 +3866,33 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI8" s="35"/>
+      <c r="DI8" s="31"/>
+      <c r="DJ8" s="70"/>
+      <c r="DK8" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL8" s="31"/>
+      <c r="DM8" s="70"/>
+      <c r="DN8" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO8" s="31"/>
+      <c r="DP8" s="70"/>
+      <c r="DQ8" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR8" s="31"/>
+      <c r="DS8" s="70"/>
+      <c r="DT8" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU8" s="35"/>
     </row>
-    <row r="9" spans="1:113" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="94" t="s">
         <v>219</v>
       </c>
@@ -3610,7 +3909,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>L4</v>
       </c>
       <c r="G9" s="5">
@@ -3646,7 +3945,7 @@
         <v>3</v>
       </c>
       <c r="Q9" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>6.6666666666666596E-2</v>
       </c>
       <c r="R9" s="6" t="s">
@@ -3671,7 +3970,7 @@
       <c r="AA9" s="20"/>
       <c r="AB9" s="20"/>
       <c r="AC9" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AD9" s="20"/>
@@ -3835,9 +4134,33 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI9" s="35"/>
+      <c r="DI9" s="31"/>
+      <c r="DJ9" s="56"/>
+      <c r="DK9" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL9" s="31"/>
+      <c r="DM9" s="56"/>
+      <c r="DN9" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO9" s="31"/>
+      <c r="DP9" s="56"/>
+      <c r="DQ9" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR9" s="31"/>
+      <c r="DS9" s="56"/>
+      <c r="DT9" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU9" s="35"/>
     </row>
-    <row r="10" spans="1:113" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="94" t="s">
         <v>219</v>
       </c>
@@ -3854,7 +4177,7 @@
         <v>6</v>
       </c>
       <c r="F10" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>D6</v>
       </c>
       <c r="G10" s="5">
@@ -3890,7 +4213,7 @@
         <v>4</v>
       </c>
       <c r="Q10" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>6.1111111111111061E-2</v>
       </c>
       <c r="R10" s="6" t="s">
@@ -3915,7 +4238,7 @@
       <c r="AA10" s="20"/>
       <c r="AB10" s="20"/>
       <c r="AC10" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AD10" s="20"/>
@@ -4079,9 +4402,33 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI10" s="35"/>
+      <c r="DI10" s="31"/>
+      <c r="DJ10" s="34"/>
+      <c r="DK10" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL10" s="31"/>
+      <c r="DM10" s="34"/>
+      <c r="DN10" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO10" s="31"/>
+      <c r="DP10" s="34"/>
+      <c r="DQ10" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR10" s="31"/>
+      <c r="DS10" s="34"/>
+      <c r="DT10" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU10" s="35"/>
     </row>
-    <row r="11" spans="1:113" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:125" x14ac:dyDescent="0.35">
       <c r="A11" s="94" t="s">
         <v>219</v>
       </c>
@@ -4098,7 +4445,7 @@
         <v>6</v>
       </c>
       <c r="F11" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>L6</v>
       </c>
       <c r="G11" s="5">
@@ -4134,7 +4481,7 @@
         <v>2</v>
       </c>
       <c r="Q11" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>8.4027777777777757E-2</v>
       </c>
       <c r="R11" s="6" t="s">
@@ -4163,7 +4510,7 @@
       <c r="AA11" s="20"/>
       <c r="AB11" s="20"/>
       <c r="AC11" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.3368055555555557E-2</v>
       </c>
       <c r="AD11" s="20">
@@ -4347,9 +4694,33 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI11" s="35"/>
+      <c r="DI11" s="31"/>
+      <c r="DJ11" s="34"/>
+      <c r="DK11" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL11" s="31"/>
+      <c r="DM11" s="34"/>
+      <c r="DN11" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO11" s="31"/>
+      <c r="DP11" s="34"/>
+      <c r="DQ11" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR11" s="31"/>
+      <c r="DS11" s="34"/>
+      <c r="DT11" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU11" s="35"/>
     </row>
-    <row r="12" spans="1:113" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:125" x14ac:dyDescent="0.35">
       <c r="A12" s="94" t="s">
         <v>219</v>
       </c>
@@ -4366,7 +4737,7 @@
         <v>3</v>
       </c>
       <c r="F12" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>E3</v>
       </c>
       <c r="G12" s="5">
@@ -4402,7 +4773,7 @@
         <v>4</v>
       </c>
       <c r="Q12" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>8.680555555555558E-2</v>
       </c>
       <c r="R12" s="6" t="s">
@@ -4433,7 +4804,7 @@
       <c r="AA12" s="20"/>
       <c r="AB12" s="20"/>
       <c r="AC12" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.8194444444444438E-2</v>
       </c>
       <c r="AD12" s="20">
@@ -4617,9 +4988,41 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI12" s="35"/>
+      <c r="DI12" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ12" s="70">
+        <v>6.0416666666666665E-3</v>
+      </c>
+      <c r="DK12" s="33">
+        <f t="shared" si="26"/>
+        <v>1.9907407407407408E-3</v>
+      </c>
+      <c r="DL12" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM12" s="70">
+        <v>1.5844907407407408E-2</v>
+      </c>
+      <c r="DN12" s="33">
+        <f t="shared" si="27"/>
+        <v>1.1793981481481482E-2</v>
+      </c>
+      <c r="DO12" s="31"/>
+      <c r="DP12" s="70"/>
+      <c r="DQ12" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR12" s="31"/>
+      <c r="DS12" s="70"/>
+      <c r="DT12" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU12" s="35"/>
     </row>
-    <row r="13" spans="1:113" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:125" x14ac:dyDescent="0.35">
       <c r="A13" s="94" t="s">
         <v>219</v>
       </c>
@@ -4636,7 +5039,7 @@
         <v>5</v>
       </c>
       <c r="F13" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>D5</v>
       </c>
       <c r="G13" s="5">
@@ -4672,7 +5075,7 @@
         <v>3</v>
       </c>
       <c r="Q13" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>7.0833333333333415E-2</v>
       </c>
       <c r="R13" s="6" t="s">
@@ -4703,7 +5106,7 @@
       <c r="AA13" s="20"/>
       <c r="AB13" s="20"/>
       <c r="AC13" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>4.5370370370370366E-2</v>
       </c>
       <c r="AD13" s="20">
@@ -4877,9 +5280,33 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI13" s="35"/>
+      <c r="DI13" s="31"/>
+      <c r="DJ13" s="32"/>
+      <c r="DK13" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL13" s="31"/>
+      <c r="DM13" s="32"/>
+      <c r="DN13" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO13" s="31"/>
+      <c r="DP13" s="32"/>
+      <c r="DQ13" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR13" s="31"/>
+      <c r="DS13" s="32"/>
+      <c r="DT13" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU13" s="35"/>
     </row>
-    <row r="14" spans="1:113" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:125" x14ac:dyDescent="0.35">
       <c r="A14" s="94" t="s">
         <v>219</v>
       </c>
@@ -4896,7 +5323,7 @@
         <v>5</v>
       </c>
       <c r="F14" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>L5</v>
       </c>
       <c r="G14" s="5">
@@ -4932,7 +5359,7 @@
         <v>2</v>
       </c>
       <c r="Q14" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>7.0833333333333415E-2</v>
       </c>
       <c r="R14" s="6" t="s">
@@ -4961,7 +5388,7 @@
       <c r="AA14" s="20"/>
       <c r="AB14" s="20"/>
       <c r="AC14" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>4.3460648148148151E-2</v>
       </c>
       <c r="AD14" s="20">
@@ -4969,7 +5396,7 @@
       </c>
       <c r="AE14" s="20"/>
       <c r="AF14" s="20">
-        <f t="shared" ref="AF14:AF24" si="29">AC14-AD14-AE14</f>
+        <f t="shared" ref="AF14:AF24" si="33">AC14-AD14-AE14</f>
         <v>4.0451388888888891E-2</v>
       </c>
       <c r="AG14" s="21">
@@ -4988,7 +5415,7 @@
       <c r="AL14" s="31"/>
       <c r="AM14" s="32"/>
       <c r="AN14" s="33" t="str">
-        <f t="shared" ref="AN14:AN24" si="30">IF(AL14=0,"NA",AM14-$AD14)</f>
+        <f t="shared" ref="AN14:AN24" si="34">IF(AL14=0,"NA",AM14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AO14" s="31">
@@ -4998,19 +5425,19 @@
         <v>8.7847222222222233E-3</v>
       </c>
       <c r="AQ14" s="33">
-        <f t="shared" ref="AQ14:AQ24" si="31">IF(AO14=0,"NA",AP14-$AD14)</f>
+        <f t="shared" ref="AQ14:AQ24" si="35">IF(AO14=0,"NA",AP14-$AD14)</f>
         <v>5.7754629629629649E-3</v>
       </c>
       <c r="AR14" s="31"/>
       <c r="AS14" s="32"/>
       <c r="AT14" s="33" t="str">
-        <f t="shared" ref="AT14:AT24" si="32">IF(AR14=0,"NA",AS14-$AD14)</f>
+        <f t="shared" ref="AT14:AT24" si="36">IF(AR14=0,"NA",AS14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AU14" s="31"/>
       <c r="AV14" s="32"/>
       <c r="AW14" s="33" t="str">
-        <f t="shared" ref="AW14:AW24" si="33">IF(AU14=0,"NA",AV14-$AD14)</f>
+        <f t="shared" ref="AW14:AW24" si="37">IF(AU14=0,"NA",AV14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AX14" s="31"/>
@@ -5026,43 +5453,43 @@
         <v>2.1307870370370369E-2</v>
       </c>
       <c r="BC14" s="33">
-        <f t="shared" ref="BC14:BC24" si="34">IF(BA14=0,"NA",BB14-$AD14)</f>
+        <f t="shared" ref="BC14:BC24" si="38">IF(BA14=0,"NA",BB14-$AD14)</f>
         <v>1.8298611111111109E-2</v>
       </c>
       <c r="BD14" s="31"/>
       <c r="BE14" s="32"/>
       <c r="BF14" s="33" t="str">
-        <f t="shared" ref="BF14:BF24" si="35">IF(BD14=0,"NA",BE14-$AD14)</f>
+        <f t="shared" ref="BF14:BF24" si="39">IF(BD14=0,"NA",BE14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BG14" s="31"/>
       <c r="BH14" s="34"/>
       <c r="BI14" s="33" t="str">
-        <f t="shared" ref="BI14:BI24" si="36">IF(BG14=0,"NA",BH14-$AD14)</f>
+        <f t="shared" ref="BI14:BI24" si="40">IF(BG14=0,"NA",BH14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BJ14" s="31"/>
       <c r="BK14" s="34"/>
       <c r="BL14" s="33" t="str">
-        <f t="shared" ref="BL14:BL24" si="37">IF(BJ14=0,"NA",BK14-$AD14)</f>
+        <f t="shared" ref="BL14:BL24" si="41">IF(BJ14=0,"NA",BK14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BM14" s="31"/>
       <c r="BN14" s="32"/>
       <c r="BO14" s="33" t="str">
-        <f t="shared" ref="BO14:BO24" si="38">IF(BM14=0,"NA",BN14-$AD14)</f>
+        <f t="shared" ref="BO14:BO24" si="42">IF(BM14=0,"NA",BN14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BP14" s="31"/>
       <c r="BQ14" s="32"/>
       <c r="BR14" s="33" t="str">
-        <f t="shared" ref="BR14:BR24" si="39">IF(BP14=0,"NA",BQ14-$AD14)</f>
+        <f t="shared" ref="BR14:BR24" si="43">IF(BP14=0,"NA",BQ14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BS14" s="31"/>
       <c r="BT14" s="34"/>
       <c r="BU14" s="33" t="str">
-        <f t="shared" ref="BU14:BU24" si="40">IF(BS14=0,"NA",BT14-$AD14)</f>
+        <f t="shared" ref="BU14:BU24" si="44">IF(BS14=0,"NA",BT14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BV14" s="31"/>
@@ -5144,12 +5571,36 @@
       <c r="DF14" s="31"/>
       <c r="DG14" s="34"/>
       <c r="DH14" s="33" t="str">
-        <f t="shared" ref="DH14:DH24" si="41">IF(DF14=0,"NA",DG14-$AD14)</f>
-        <v>NA</v>
-      </c>
-      <c r="DI14" s="35"/>
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI14" s="31"/>
+      <c r="DJ14" s="32"/>
+      <c r="DK14" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL14" s="31"/>
+      <c r="DM14" s="34"/>
+      <c r="DN14" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO14" s="31"/>
+      <c r="DP14" s="34"/>
+      <c r="DQ14" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR14" s="31"/>
+      <c r="DS14" s="34"/>
+      <c r="DT14" s="33" t="str">
+        <f t="shared" ref="DT14:DT24" si="45">IF(DR14=0,"NA",DS14-$AD14)</f>
+        <v>NA</v>
+      </c>
+      <c r="DU14" s="35"/>
     </row>
-    <row r="15" spans="1:113" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:125" x14ac:dyDescent="0.35">
       <c r="A15" s="94" t="s">
         <v>219</v>
       </c>
@@ -5166,7 +5617,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>L4</v>
       </c>
       <c r="G15" s="5">
@@ -5202,7 +5653,7 @@
         <v>3</v>
       </c>
       <c r="Q15" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>5.9027777777777735E-2</v>
       </c>
       <c r="R15" s="6" t="s">
@@ -5233,7 +5684,7 @@
       <c r="AA15" s="20"/>
       <c r="AB15" s="20"/>
       <c r="AC15" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>4.8969907407407406E-2</v>
       </c>
       <c r="AD15" s="20">
@@ -5243,7 +5694,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="AF15" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.1643518518518517E-2</v>
       </c>
       <c r="AG15" s="21">
@@ -5254,7 +5705,7 @@
       </c>
       <c r="AI15" s="22"/>
       <c r="AJ15" s="32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK15" s="30">
         <v>5</v>
@@ -5262,7 +5713,7 @@
       <c r="AL15" s="31"/>
       <c r="AM15" s="34"/>
       <c r="AN15" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AO15" s="31">
@@ -5272,19 +5723,19 @@
         <v>7.6273148148148151E-3</v>
       </c>
       <c r="AQ15" s="33">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>3.7731481481481483E-3</v>
       </c>
       <c r="AR15" s="31"/>
       <c r="AS15" s="32"/>
       <c r="AT15" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU15" s="31"/>
       <c r="AV15" s="32"/>
       <c r="AW15" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX15" s="31"/>
@@ -5296,19 +5747,19 @@
       <c r="BA15" s="31"/>
       <c r="BB15" s="32"/>
       <c r="BC15" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BD15" s="31"/>
       <c r="BE15" s="32"/>
       <c r="BF15" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG15" s="31"/>
       <c r="BH15" s="34"/>
       <c r="BI15" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ15" s="31">
@@ -5318,25 +5769,25 @@
         <v>1.7777777777777778E-2</v>
       </c>
       <c r="BL15" s="33">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>1.3923611111111111E-2</v>
       </c>
       <c r="BM15" s="31"/>
       <c r="BN15" s="32"/>
       <c r="BO15" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BP15" s="31"/>
       <c r="BQ15" s="32"/>
       <c r="BR15" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS15" s="31"/>
       <c r="BT15" s="34"/>
       <c r="BU15" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV15" s="31">
@@ -5422,12 +5873,40 @@
       <c r="DF15" s="31"/>
       <c r="DG15" s="34"/>
       <c r="DH15" s="33" t="str">
-        <f t="shared" si="41"/>
-        <v>NA</v>
-      </c>
-      <c r="DI15" s="35"/>
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI15" s="31"/>
+      <c r="DJ15" s="32"/>
+      <c r="DK15" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL15" s="31"/>
+      <c r="DM15" s="34"/>
+      <c r="DN15" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO15" s="31">
+        <v>2</v>
+      </c>
+      <c r="DP15" s="34">
+        <v>1.5960648148148147E-2</v>
+      </c>
+      <c r="DQ15" s="33">
+        <f t="shared" si="28"/>
+        <v>1.210648148148148E-2</v>
+      </c>
+      <c r="DR15" s="31"/>
+      <c r="DS15" s="34"/>
+      <c r="DT15" s="33" t="str">
+        <f t="shared" si="45"/>
+        <v>NA</v>
+      </c>
+      <c r="DU15" s="35"/>
     </row>
-    <row r="16" spans="1:113" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:125" x14ac:dyDescent="0.35">
       <c r="A16" s="94" t="s">
         <v>219</v>
       </c>
@@ -5444,7 +5923,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>E1</v>
       </c>
       <c r="G16" s="5">
@@ -5480,7 +5959,7 @@
         <v>4</v>
       </c>
       <c r="Q16" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>8.9583333333333237E-2</v>
       </c>
       <c r="R16" s="6" t="s">
@@ -5511,7 +5990,7 @@
       <c r="AA16" s="20"/>
       <c r="AB16" s="20"/>
       <c r="AC16" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>6.0636574074074072E-2</v>
       </c>
       <c r="AD16" s="20">
@@ -5521,7 +6000,7 @@
         <v>1.4016203703703704E-2</v>
       </c>
       <c r="AF16" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.2453703703703702E-2</v>
       </c>
       <c r="AG16" s="21">
@@ -5532,33 +6011,33 @@
       </c>
       <c r="AI16" s="22"/>
       <c r="AJ16" s="32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK16" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL16" s="31"/>
       <c r="AM16" s="34"/>
       <c r="AN16" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AO16" s="31"/>
       <c r="AP16" s="34"/>
       <c r="AQ16" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AR16" s="31"/>
       <c r="AS16" s="34"/>
       <c r="AT16" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU16" s="31"/>
       <c r="AV16" s="34"/>
       <c r="AW16" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX16" s="31"/>
@@ -5570,19 +6049,19 @@
       <c r="BA16" s="31"/>
       <c r="BB16" s="34"/>
       <c r="BC16" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BD16" s="31"/>
       <c r="BE16" s="34"/>
       <c r="BF16" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG16" s="31"/>
       <c r="BH16" s="34"/>
       <c r="BI16" s="56" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ16" s="31">
@@ -5592,25 +6071,25 @@
         <v>4.1666666666666666E-3</v>
       </c>
       <c r="BL16" s="33">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BM16" s="31"/>
       <c r="BN16" s="32"/>
       <c r="BO16" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BP16" s="31"/>
       <c r="BQ16" s="32"/>
       <c r="BR16" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS16" s="31"/>
       <c r="BT16" s="56"/>
       <c r="BU16" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV16" s="31"/>
@@ -5677,11 +6156,15 @@
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
-      <c r="CZ16" s="31"/>
-      <c r="DA16" s="34"/>
-      <c r="DB16" s="33" t="str">
+      <c r="CZ16" s="31">
+        <v>1</v>
+      </c>
+      <c r="DA16" s="34">
+        <v>1.0266203703703704E-2</v>
+      </c>
+      <c r="DB16" s="33">
         <f t="shared" si="23"/>
-        <v>NA</v>
+        <v>6.0995370370370379E-3</v>
       </c>
       <c r="DC16" s="31"/>
       <c r="DD16" s="34"/>
@@ -5696,12 +6179,44 @@
         <v>4.6064814814814814E-3</v>
       </c>
       <c r="DH16" s="33">
-        <f t="shared" si="41"/>
+        <f t="shared" si="25"/>
         <v>4.3981481481481476E-4</v>
       </c>
-      <c r="DI16" s="35"/>
+      <c r="DI16" s="31">
+        <v>2</v>
+      </c>
+      <c r="DJ16" s="34">
+        <v>8.1481481481481474E-3</v>
+      </c>
+      <c r="DK16" s="33">
+        <f t="shared" si="26"/>
+        <v>3.9814814814814808E-3</v>
+      </c>
+      <c r="DL16" s="31">
+        <v>2</v>
+      </c>
+      <c r="DM16" s="34">
+        <v>4.1666666666666666E-3</v>
+      </c>
+      <c r="DN16" s="33">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="DO16" s="31"/>
+      <c r="DP16" s="34"/>
+      <c r="DQ16" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR16" s="31"/>
+      <c r="DS16" s="34"/>
+      <c r="DT16" s="33" t="str">
+        <f t="shared" si="45"/>
+        <v>NA</v>
+      </c>
+      <c r="DU16" s="35"/>
     </row>
-    <row r="17" spans="1:113" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:125" x14ac:dyDescent="0.35">
       <c r="A17" s="94" t="s">
         <v>219</v>
       </c>
@@ -5718,7 +6233,7 @@
         <v>6</v>
       </c>
       <c r="F17" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>D6</v>
       </c>
       <c r="G17" s="5">
@@ -5754,7 +6269,7 @@
         <v>4</v>
       </c>
       <c r="Q17" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>5.7638888888888851E-2</v>
       </c>
       <c r="R17" s="6" t="s">
@@ -5787,7 +6302,7 @@
       <c r="AA17" s="20"/>
       <c r="AB17" s="20"/>
       <c r="AC17" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.9444444444444439E-2</v>
       </c>
       <c r="AD17" s="20">
@@ -5797,7 +6312,7 @@
         <v>1.1388888888888888E-2</v>
       </c>
       <c r="AF17" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.4259259259259255E-2</v>
       </c>
       <c r="AG17" s="21">
@@ -5816,25 +6331,25 @@
       <c r="AL17" s="31"/>
       <c r="AM17" s="34"/>
       <c r="AN17" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AO17" s="31"/>
       <c r="AP17" s="34"/>
       <c r="AQ17" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AR17" s="31"/>
       <c r="AS17" s="34"/>
       <c r="AT17" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU17" s="31"/>
       <c r="AV17" s="34"/>
       <c r="AW17" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX17" s="31"/>
@@ -5850,19 +6365,19 @@
         <v>3.7962962962962963E-3</v>
       </c>
       <c r="BC17" s="33">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="BD17" s="31"/>
       <c r="BE17" s="34"/>
       <c r="BF17" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG17" s="31"/>
       <c r="BH17" s="34"/>
       <c r="BI17" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ17" s="31">
@@ -5872,25 +6387,25 @@
         <v>2.4710648148148148E-2</v>
       </c>
       <c r="BL17" s="33">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>2.0914351851851851E-2</v>
       </c>
       <c r="BM17" s="31"/>
       <c r="BN17" s="34"/>
       <c r="BO17" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BP17" s="31"/>
       <c r="BQ17" s="34"/>
       <c r="BR17" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS17" s="31"/>
       <c r="BT17" s="32"/>
       <c r="BU17" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV17" s="31"/>
@@ -5972,12 +6487,40 @@
       <c r="DF17" s="31"/>
       <c r="DG17" s="34"/>
       <c r="DH17" s="33" t="str">
-        <f t="shared" si="41"/>
-        <v>NA</v>
-      </c>
-      <c r="DI17" s="35"/>
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI17" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ17" s="34">
+        <v>1.1331018518518518E-2</v>
+      </c>
+      <c r="DK17" s="33">
+        <f t="shared" si="26"/>
+        <v>7.5347222222222222E-3</v>
+      </c>
+      <c r="DL17" s="31"/>
+      <c r="DM17" s="34"/>
+      <c r="DN17" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO17" s="31"/>
+      <c r="DP17" s="34"/>
+      <c r="DQ17" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR17" s="31"/>
+      <c r="DS17" s="34"/>
+      <c r="DT17" s="33" t="str">
+        <f t="shared" si="45"/>
+        <v>NA</v>
+      </c>
+      <c r="DU17" s="35"/>
     </row>
-    <row r="18" spans="1:113" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:125" x14ac:dyDescent="0.35">
       <c r="A18" s="94" t="s">
         <v>219</v>
       </c>
@@ -5994,7 +6537,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>E2</v>
       </c>
       <c r="G18" s="5">
@@ -6030,7 +6573,7 @@
         <v>3</v>
       </c>
       <c r="Q18" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>9.2361111111111116E-2</v>
       </c>
       <c r="R18" s="6" t="s">
@@ -6059,7 +6602,7 @@
       <c r="AA18" s="20"/>
       <c r="AB18" s="20"/>
       <c r="AC18" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>4.3784722222222218E-2</v>
       </c>
       <c r="AD18" s="20">
@@ -6067,7 +6610,7 @@
       </c>
       <c r="AE18" s="20"/>
       <c r="AF18" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.1006944444444443E-2</v>
       </c>
       <c r="AG18" s="21">
@@ -6078,10 +6621,10 @@
       </c>
       <c r="AI18" s="22"/>
       <c r="AJ18" s="32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK18" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL18" s="31">
         <v>1</v>
@@ -6090,25 +6633,25 @@
         <v>1.726851851851852E-2</v>
       </c>
       <c r="AN18" s="33">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1.4490740740740742E-2</v>
       </c>
       <c r="AO18" s="31"/>
       <c r="AP18" s="34"/>
       <c r="AQ18" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AR18" s="31"/>
       <c r="AS18" s="34"/>
       <c r="AT18" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU18" s="31"/>
       <c r="AV18" s="34"/>
       <c r="AW18" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX18" s="31"/>
@@ -6120,19 +6663,19 @@
       <c r="BA18" s="31"/>
       <c r="BB18" s="34"/>
       <c r="BC18" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BD18" s="31"/>
       <c r="BE18" s="34"/>
       <c r="BF18" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG18" s="31"/>
       <c r="BH18" s="34"/>
       <c r="BI18" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ18" s="31">
@@ -6142,19 +6685,19 @@
         <v>2.8240740740740739E-3</v>
       </c>
       <c r="BL18" s="33">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>4.6296296296296016E-5</v>
       </c>
       <c r="BM18" s="31"/>
       <c r="BN18" s="34"/>
       <c r="BO18" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BP18" s="31"/>
       <c r="BQ18" s="34"/>
       <c r="BR18" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS18" s="31">
@@ -6164,7 +6707,7 @@
         <v>1.6076388888888887E-2</v>
       </c>
       <c r="BU18" s="33">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>1.3298611111111108E-2</v>
       </c>
       <c r="BV18" s="31"/>
@@ -6227,11 +6770,15 @@
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
-      <c r="CZ18" s="31"/>
-      <c r="DA18" s="34"/>
-      <c r="DB18" s="33" t="str">
+      <c r="CZ18" s="31">
+        <v>1</v>
+      </c>
+      <c r="DA18" s="34">
+        <v>4.6759259259259263E-3</v>
+      </c>
+      <c r="DB18" s="33">
         <f t="shared" si="23"/>
-        <v>NA</v>
+        <v>1.8981481481481484E-3</v>
       </c>
       <c r="DC18" s="31"/>
       <c r="DD18" s="34"/>
@@ -6242,12 +6789,44 @@
       <c r="DF18" s="31"/>
       <c r="DG18" s="34"/>
       <c r="DH18" s="33" t="str">
-        <f t="shared" si="41"/>
-        <v>NA</v>
-      </c>
-      <c r="DI18" s="35"/>
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI18" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ18" s="34">
+        <v>2.5173611111111112E-2</v>
+      </c>
+      <c r="DK18" s="33">
+        <f t="shared" si="26"/>
+        <v>2.2395833333333334E-2</v>
+      </c>
+      <c r="DL18" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM18" s="34">
+        <v>2.8356481481481483E-3</v>
+      </c>
+      <c r="DN18" s="33">
+        <f t="shared" si="27"/>
+        <v>5.7870370370370454E-5</v>
+      </c>
+      <c r="DO18" s="31"/>
+      <c r="DP18" s="34"/>
+      <c r="DQ18" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR18" s="31"/>
+      <c r="DS18" s="34"/>
+      <c r="DT18" s="33" t="str">
+        <f t="shared" si="45"/>
+        <v>NA</v>
+      </c>
+      <c r="DU18" s="35"/>
     </row>
-    <row r="19" spans="1:113" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:125" x14ac:dyDescent="0.35">
       <c r="A19" s="94" t="s">
         <v>219</v>
       </c>
@@ -6264,7 +6843,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>D3</v>
       </c>
       <c r="G19" s="5">
@@ -6300,7 +6879,7 @@
         <v>5</v>
       </c>
       <c r="Q19" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>0.1069444444444444</v>
       </c>
       <c r="R19" s="6" t="s">
@@ -6335,7 +6914,7 @@
       </c>
       <c r="AB19" s="20"/>
       <c r="AC19" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>6.7708333333333329E-2</v>
       </c>
       <c r="AD19" s="20">
@@ -6345,7 +6924,7 @@
         <v>1.9652777777777779E-2</v>
       </c>
       <c r="AF19" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.4062499999999991E-2</v>
       </c>
       <c r="AG19" s="21">
@@ -6364,7 +6943,7 @@
       <c r="AL19" s="31"/>
       <c r="AM19" s="34"/>
       <c r="AN19" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AO19" s="31">
@@ -6374,19 +6953,19 @@
         <v>2.7662037037037041E-2</v>
       </c>
       <c r="AQ19" s="33">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>2.3668981481481485E-2</v>
       </c>
       <c r="AR19" s="31"/>
       <c r="AS19" s="34"/>
       <c r="AT19" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU19" s="31"/>
       <c r="AV19" s="34"/>
       <c r="AW19" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX19" s="31"/>
@@ -6398,19 +6977,19 @@
       <c r="BA19" s="31"/>
       <c r="BB19" s="34"/>
       <c r="BC19" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BD19" s="31"/>
       <c r="BE19" s="34"/>
       <c r="BF19" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG19" s="31"/>
       <c r="BH19" s="34"/>
       <c r="BI19" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ19" s="31">
@@ -6420,25 +6999,25 @@
         <v>7.2337962962962963E-3</v>
       </c>
       <c r="BL19" s="33">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>3.2407407407407402E-3</v>
       </c>
       <c r="BM19" s="31"/>
       <c r="BN19" s="34"/>
       <c r="BO19" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BP19" s="31"/>
       <c r="BQ19" s="34"/>
       <c r="BR19" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS19" s="31"/>
       <c r="BT19" s="32"/>
       <c r="BU19" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV19" s="31"/>
@@ -6520,12 +7099,36 @@
       <c r="DF19" s="31"/>
       <c r="DG19" s="34"/>
       <c r="DH19" s="33" t="str">
-        <f t="shared" si="41"/>
-        <v>NA</v>
-      </c>
-      <c r="DI19" s="35"/>
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI19" s="31"/>
+      <c r="DJ19" s="34"/>
+      <c r="DK19" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL19" s="31"/>
+      <c r="DM19" s="34"/>
+      <c r="DN19" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO19" s="31"/>
+      <c r="DP19" s="34"/>
+      <c r="DQ19" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR19" s="31"/>
+      <c r="DS19" s="34"/>
+      <c r="DT19" s="33" t="str">
+        <f t="shared" si="45"/>
+        <v>NA</v>
+      </c>
+      <c r="DU19" s="35"/>
     </row>
-    <row r="20" spans="1:113" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:125" x14ac:dyDescent="0.35">
       <c r="A20" s="94" t="s">
         <v>219</v>
       </c>
@@ -6542,7 +7145,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>D2</v>
       </c>
       <c r="G20" s="5">
@@ -6578,7 +7181,7 @@
         <v>3</v>
       </c>
       <c r="Q20" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>9.8611111111111038E-2</v>
       </c>
       <c r="R20" s="6" t="s">
@@ -6607,7 +7210,7 @@
       <c r="AA20" s="20"/>
       <c r="AB20" s="20"/>
       <c r="AC20" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>4.221064814814815E-2</v>
       </c>
       <c r="AD20" s="20">
@@ -6615,7 +7218,7 @@
       </c>
       <c r="AE20" s="20"/>
       <c r="AF20" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>3.8738425925925926E-2</v>
       </c>
       <c r="AG20" s="21">
@@ -6634,25 +7237,25 @@
       <c r="AL20" s="31"/>
       <c r="AM20" s="34"/>
       <c r="AN20" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AO20" s="31"/>
       <c r="AP20" s="34"/>
       <c r="AQ20" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AR20" s="31"/>
       <c r="AS20" s="34"/>
       <c r="AT20" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU20" s="31"/>
       <c r="AV20" s="34"/>
       <c r="AW20" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX20" s="31"/>
@@ -6664,19 +7267,19 @@
       <c r="BA20" s="31"/>
       <c r="BB20" s="34"/>
       <c r="BC20" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BD20" s="31"/>
       <c r="BE20" s="34"/>
       <c r="BF20" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG20" s="31"/>
       <c r="BH20" s="34"/>
       <c r="BI20" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ20" s="31">
@@ -6686,25 +7289,25 @@
         <v>3.7731481481481483E-3</v>
       </c>
       <c r="BL20" s="33">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>3.0092592592592627E-4</v>
       </c>
       <c r="BM20" s="31"/>
       <c r="BN20" s="34"/>
       <c r="BO20" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BP20" s="31"/>
       <c r="BQ20" s="34"/>
       <c r="BR20" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS20" s="31"/>
       <c r="BT20" s="34"/>
       <c r="BU20" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV20" s="31"/>
@@ -6782,12 +7385,36 @@
       <c r="DF20" s="31"/>
       <c r="DG20" s="34"/>
       <c r="DH20" s="33" t="str">
-        <f t="shared" si="41"/>
-        <v>NA</v>
-      </c>
-      <c r="DI20" s="35"/>
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI20" s="31"/>
+      <c r="DJ20" s="34"/>
+      <c r="DK20" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL20" s="31"/>
+      <c r="DM20" s="34"/>
+      <c r="DN20" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO20" s="31"/>
+      <c r="DP20" s="34"/>
+      <c r="DQ20" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR20" s="31"/>
+      <c r="DS20" s="34"/>
+      <c r="DT20" s="33" t="str">
+        <f t="shared" si="45"/>
+        <v>NA</v>
+      </c>
+      <c r="DU20" s="35"/>
     </row>
-    <row r="21" spans="1:113" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:125" x14ac:dyDescent="0.35">
       <c r="A21" s="94" t="s">
         <v>219</v>
       </c>
@@ -6804,7 +7431,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>L2</v>
       </c>
       <c r="G21" s="5">
@@ -6840,7 +7467,7 @@
         <v>5</v>
       </c>
       <c r="Q21" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>7.7777777777777724E-2</v>
       </c>
       <c r="R21" s="5" t="s">
@@ -6873,7 +7500,7 @@
       </c>
       <c r="AB21" s="77"/>
       <c r="AC21" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>7.5497685185185195E-2</v>
       </c>
       <c r="AD21" s="78">
@@ -6883,7 +7510,7 @@
         <v>2.7743055555555559E-2</v>
       </c>
       <c r="AF21" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.2511574074074077E-2</v>
       </c>
       <c r="AG21" s="21">
@@ -6894,37 +7521,37 @@
       </c>
       <c r="AI21" s="22"/>
       <c r="AJ21" s="32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AK21" s="30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL21" s="31"/>
       <c r="AM21" s="32"/>
       <c r="AN21" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AO21" s="31">
         <v>41</v>
       </c>
       <c r="AP21" s="34">
-        <v>9.0046296296296298E-3</v>
+        <v>8.2175925925925923E-3</v>
       </c>
       <c r="AQ21" s="33">
-        <f t="shared" si="31"/>
-        <v>3.7615740740740743E-3</v>
+        <f t="shared" si="35"/>
+        <v>2.9745370370370368E-3</v>
       </c>
       <c r="AR21" s="31"/>
       <c r="AS21" s="32"/>
       <c r="AT21" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU21" s="31"/>
       <c r="AV21" s="32"/>
       <c r="AW21" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX21" s="31"/>
@@ -6936,19 +7563,19 @@
       <c r="BA21" s="31"/>
       <c r="BB21" s="34"/>
       <c r="BC21" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BD21" s="31"/>
       <c r="BE21" s="32"/>
       <c r="BF21" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG21" s="31"/>
       <c r="BH21" s="32"/>
       <c r="BI21" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ21" s="31">
@@ -6958,19 +7585,19 @@
         <v>7.1874999999999994E-3</v>
       </c>
       <c r="BL21" s="33">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>1.944444444444444E-3</v>
       </c>
       <c r="BM21" s="31"/>
       <c r="BN21" s="32"/>
       <c r="BO21" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BP21" s="31"/>
       <c r="BQ21" s="32"/>
       <c r="BR21" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS21" s="31">
@@ -6980,7 +7607,7 @@
         <v>2.6122685185185186E-2</v>
       </c>
       <c r="BU21" s="33">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>2.087962962962963E-2</v>
       </c>
       <c r="BV21" s="31"/>
@@ -7066,12 +7693,48 @@
       <c r="DF21" s="31"/>
       <c r="DG21" s="56"/>
       <c r="DH21" s="33" t="str">
-        <f t="shared" si="41"/>
-        <v>NA</v>
-      </c>
-      <c r="DI21" s="35"/>
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI21" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ21" s="34">
+        <v>5.6249999999999998E-3</v>
+      </c>
+      <c r="DK21" s="33">
+        <f t="shared" si="26"/>
+        <v>3.819444444444443E-4</v>
+      </c>
+      <c r="DL21" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM21" s="56">
+        <v>8.2291666666666659E-3</v>
+      </c>
+      <c r="DN21" s="33">
+        <f t="shared" si="27"/>
+        <v>2.9861111111111104E-3</v>
+      </c>
+      <c r="DO21" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP21" s="56">
+        <v>9.8726851851851857E-3</v>
+      </c>
+      <c r="DQ21" s="33">
+        <f t="shared" si="28"/>
+        <v>4.6296296296296302E-3</v>
+      </c>
+      <c r="DR21" s="31"/>
+      <c r="DS21" s="56"/>
+      <c r="DT21" s="33" t="str">
+        <f t="shared" si="45"/>
+        <v>NA</v>
+      </c>
+      <c r="DU21" s="35"/>
     </row>
-    <row r="22" spans="1:113" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="94" t="s">
         <v>219</v>
       </c>
@@ -7088,7 +7751,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>L1</v>
       </c>
       <c r="G22" s="5">
@@ -7124,7 +7787,7 @@
         <v>3</v>
       </c>
       <c r="Q22" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>7.3611111111111127E-2</v>
       </c>
       <c r="R22" s="5" t="s">
@@ -7153,7 +7816,7 @@
       <c r="AA22" s="77"/>
       <c r="AB22" s="77"/>
       <c r="AC22" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.2326388888888895E-2</v>
       </c>
       <c r="AD22" s="78">
@@ -7163,7 +7826,7 @@
         <v>5.6712962962962958E-3</v>
       </c>
       <c r="AF22" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.2916666666666672E-2</v>
       </c>
       <c r="AG22" s="21">
@@ -7182,25 +7845,25 @@
       <c r="AL22" s="38"/>
       <c r="AM22" s="40"/>
       <c r="AN22" s="41" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AO22" s="38"/>
       <c r="AP22" s="40"/>
       <c r="AQ22" s="41" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AR22" s="38"/>
       <c r="AS22" s="82"/>
       <c r="AT22" s="41" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU22" s="38"/>
       <c r="AV22" s="82"/>
       <c r="AW22" s="41" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX22" s="38"/>
@@ -7212,19 +7875,19 @@
       <c r="BA22" s="38"/>
       <c r="BB22" s="40"/>
       <c r="BC22" s="41" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BD22" s="38"/>
       <c r="BE22" s="82"/>
       <c r="BF22" s="41" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG22" s="38"/>
       <c r="BH22" s="82"/>
       <c r="BI22" s="41" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ22" s="38">
@@ -7234,25 +7897,25 @@
         <v>4.1782407407407402E-3</v>
       </c>
       <c r="BL22" s="41">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>4.3981481481481389E-4</v>
       </c>
       <c r="BM22" s="38"/>
       <c r="BN22" s="82"/>
       <c r="BO22" s="41" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BP22" s="38"/>
       <c r="BQ22" s="82"/>
       <c r="BR22" s="41" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS22" s="38"/>
       <c r="BT22" s="82"/>
       <c r="BU22" s="41" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV22" s="38"/>
@@ -7330,12 +7993,36 @@
       <c r="DF22" s="38"/>
       <c r="DG22" s="40"/>
       <c r="DH22" s="41" t="str">
-        <f t="shared" si="41"/>
-        <v>NA</v>
-      </c>
-      <c r="DI22" s="39"/>
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI22" s="38"/>
+      <c r="DJ22" s="40"/>
+      <c r="DK22" s="41" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL22" s="38"/>
+      <c r="DM22" s="40"/>
+      <c r="DN22" s="41" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO22" s="38"/>
+      <c r="DP22" s="40"/>
+      <c r="DQ22" s="41" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR22" s="38"/>
+      <c r="DS22" s="40"/>
+      <c r="DT22" s="41" t="str">
+        <f t="shared" si="45"/>
+        <v>NA</v>
+      </c>
+      <c r="DU22" s="39"/>
     </row>
-    <row r="23" spans="1:113" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="94" t="s">
         <v>219</v>
       </c>
@@ -7352,7 +8039,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="74" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>D1</v>
       </c>
       <c r="G23" s="5">
@@ -7388,7 +8075,7 @@
         <v>3</v>
       </c>
       <c r="Q23" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>5.8333333333333348E-2</v>
       </c>
       <c r="R23" s="6" t="s">
@@ -7417,7 +8104,7 @@
       <c r="AA23" s="77"/>
       <c r="AB23" s="77"/>
       <c r="AC23" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>4.7476851851851853E-2</v>
       </c>
       <c r="AD23" s="78">
@@ -7425,7 +8112,7 @@
       </c>
       <c r="AE23" s="21"/>
       <c r="AF23" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.356481481481482E-2</v>
       </c>
       <c r="AG23" s="21">
@@ -7444,25 +8131,25 @@
       <c r="AL23" s="32"/>
       <c r="AM23" s="32"/>
       <c r="AN23" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AO23" s="32"/>
       <c r="AP23" s="32"/>
       <c r="AQ23" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AR23" s="32"/>
       <c r="AS23" s="32"/>
       <c r="AT23" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU23" s="32"/>
       <c r="AV23" s="32"/>
       <c r="AW23" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX23" s="32"/>
@@ -7478,43 +8165,43 @@
         <v>2.3206018518518515E-2</v>
       </c>
       <c r="BC23" s="33">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1.9293981481481478E-2</v>
       </c>
       <c r="BD23" s="32"/>
       <c r="BE23" s="32"/>
       <c r="BF23" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG23" s="32"/>
       <c r="BH23" s="32"/>
       <c r="BI23" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ23" s="32"/>
       <c r="BK23" s="32"/>
       <c r="BL23" s="41" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BM23" s="32"/>
       <c r="BN23" s="32"/>
       <c r="BO23" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BP23" s="32"/>
       <c r="BQ23" s="32"/>
       <c r="BR23" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS23" s="32"/>
       <c r="BT23" s="32"/>
       <c r="BU23" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV23" s="32"/>
@@ -7592,12 +8279,40 @@
       <c r="DF23" s="32"/>
       <c r="DG23" s="32"/>
       <c r="DH23" s="33" t="str">
-        <f t="shared" si="41"/>
-        <v>NA</v>
-      </c>
-      <c r="DI23" s="32"/>
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI23" s="32">
+        <v>3</v>
+      </c>
+      <c r="DJ23" s="34">
+        <v>8.3680555555555557E-3</v>
+      </c>
+      <c r="DK23" s="33">
+        <f t="shared" si="26"/>
+        <v>4.4560185185185189E-3</v>
+      </c>
+      <c r="DL23" s="32"/>
+      <c r="DM23" s="32"/>
+      <c r="DN23" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO23" s="32"/>
+      <c r="DP23" s="32"/>
+      <c r="DQ23" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR23" s="32"/>
+      <c r="DS23" s="32"/>
+      <c r="DT23" s="33" t="str">
+        <f t="shared" si="45"/>
+        <v>NA</v>
+      </c>
+      <c r="DU23" s="32"/>
     </row>
-    <row r="24" spans="1:113" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="94" t="s">
         <v>219</v>
       </c>
@@ -7614,7 +8329,7 @@
         <v>3</v>
       </c>
       <c r="F24" s="75" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>L3</v>
       </c>
       <c r="G24" s="11">
@@ -7650,7 +8365,7 @@
         <v>3</v>
       </c>
       <c r="Q24" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>5.1388888888888873E-2</v>
       </c>
       <c r="R24" s="12" t="s">
@@ -7679,7 +8394,7 @@
       <c r="AA24" s="69"/>
       <c r="AB24" s="69"/>
       <c r="AC24" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.2789351851851851E-2</v>
       </c>
       <c r="AD24" s="80">
@@ -7689,7 +8404,7 @@
         <v>5.3240740740740748E-3</v>
       </c>
       <c r="AF24" s="23">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.355324074074074E-2</v>
       </c>
       <c r="AG24" s="24">
@@ -7712,7 +8427,7 @@
         <v>4.0729166666666664E-2</v>
       </c>
       <c r="AN24" s="33">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>3.681712962962963E-2</v>
       </c>
       <c r="AO24" s="32">
@@ -7722,19 +8437,19 @@
         <v>3.9120370370370368E-3</v>
       </c>
       <c r="AQ24" s="33">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AR24" s="32"/>
       <c r="AS24" s="32"/>
       <c r="AT24" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU24" s="32"/>
       <c r="AV24" s="32"/>
       <c r="AW24" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX24" s="32"/>
@@ -7750,19 +8465,19 @@
         <v>1.9745370370370371E-2</v>
       </c>
       <c r="BC24" s="33">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1.5833333333333335E-2</v>
       </c>
       <c r="BD24" s="32"/>
       <c r="BE24" s="32"/>
       <c r="BF24" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG24" s="32"/>
       <c r="BH24" s="32"/>
       <c r="BI24" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ24" s="31">
@@ -7772,25 +8487,25 @@
         <v>2.1944444444444447E-2</v>
       </c>
       <c r="BL24" s="41">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>1.803240740740741E-2</v>
       </c>
       <c r="BM24" s="32"/>
       <c r="BN24" s="32"/>
       <c r="BO24" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BP24" s="32"/>
       <c r="BQ24" s="32"/>
       <c r="BR24" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS24" s="32"/>
       <c r="BT24" s="32"/>
       <c r="BU24" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV24" s="32"/>
@@ -7876,14 +8591,38 @@
       <c r="DF24" s="32"/>
       <c r="DG24" s="34"/>
       <c r="DH24" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="25"/>
         <v>NA</v>
       </c>
       <c r="DI24" s="32"/>
+      <c r="DJ24" s="32"/>
+      <c r="DK24" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL24" s="32"/>
+      <c r="DM24" s="34"/>
+      <c r="DN24" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO24" s="32"/>
+      <c r="DP24" s="34"/>
+      <c r="DQ24" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR24" s="32"/>
+      <c r="DS24" s="34"/>
+      <c r="DT24" s="33" t="str">
+        <f t="shared" si="45"/>
+        <v>NA</v>
+      </c>
+      <c r="DU24" s="32"/>
     </row>
-    <row r="25" spans="1:113" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F25" s="75" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>

--- a/URUVS/Datasheets/URUV/06.2024/June_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/06.2024/June_RecordingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\06.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92DD4D42-54D5-4747-9418-97048918BBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54DB5DB6-F8DA-42C9-8F18-875CF1A394DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3840" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-9405" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -3103,10 +3103,10 @@
       </c>
       <c r="AI6" s="22"/>
       <c r="AJ6" s="32">
+        <v>7</v>
+      </c>
+      <c r="AK6" s="30">
         <v>6</v>
-      </c>
-      <c r="AK6" s="30">
-        <v>5</v>
       </c>
       <c r="AL6" s="31"/>
       <c r="AM6" s="34"/>
@@ -3120,11 +3120,15 @@
         <f t="shared" si="2"/>
         <v>NA</v>
       </c>
-      <c r="AR6" s="31"/>
-      <c r="AS6" s="32"/>
-      <c r="AT6" s="33" t="str">
+      <c r="AR6" s="31">
+        <v>53</v>
+      </c>
+      <c r="AS6" s="34">
+        <v>1.525462962962963E-2</v>
+      </c>
+      <c r="AT6" s="33">
         <f t="shared" si="3"/>
-        <v>NA</v>
+        <v>9.6990740740740752E-3</v>
       </c>
       <c r="AU6" s="31"/>
       <c r="AV6" s="32"/>
@@ -3157,7 +3161,7 @@
         <v>NA</v>
       </c>
       <c r="BJ6" s="31">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="BK6" s="34">
         <v>5.6365740740740742E-3</v>
